--- a/esyluban/examples/dev/DataTables/test/test_ref.xlsx
+++ b/esyluban/examples/dev/DataTables/test/test_ref.xlsx
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="3"/>
   <sheetData>
     <row r="1">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="test.TbTestRef" &amp; value_type="test.TestRef" &amp; read_schema_from_file="false" &amp; input="ref@test/test_ref.xlsx" &amp; output="test_tbtestref"</t>
+          <t>full_name="test.TbTestRef"</t>
         </is>
       </c>
     </row>
@@ -1432,20 +1432,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="X1:Z1"/>
@@ -1471,7 +1457,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="test.TbTestBeRef" &amp; value_type="test.TestBeRef" &amp; read_schema_from_file="false" &amp; input="be_ref1@test/test_ref.xlsx" &amp; output="test_tbtestberef"</t>
+          <t>full_name="test.TbTestBeRef"</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1587,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="test.TbTestBeRef2" &amp; value_type="test.TestBeRef" &amp; read_schema_from_file="false" &amp; input="be_ref2@test/test_ref.xlsx" &amp; output="test_tbtestberef2"</t>
+          <t>full_name="test.TbTestBeRef2" &amp; value_type="test.TestBeRef"</t>
         </is>
       </c>
     </row>

--- a/esyluban/examples/dev/DataTables/test/test_ref.xlsx
+++ b/esyluban/examples/dev/DataTables/test/test_ref.xlsx
@@ -1434,7 +1434,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="X1:Z1"/>
+    <mergeCell ref="X2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
